--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הילה רוח – זאת השנה שלי</v>
+        <v>אופיר הדס – משוגע</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%99%d7%9c%d7%94-%d7%a8%d7%95%d7%97-%d7%96%d7%90%d7%aa-%d7%94%d7%a9%d7%a0%d7%94-%d7%a9%d7%9c%d7%99/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%94%d7%93%d7%a1-%d7%9e%d7%a9%d7%95%d7%92%d7%a2/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הילה רוח שרה שיר שנשמע כמו הבטחה לעצמה, לא הכרזה חגיגית אלא ניסיון להאמין.הבלדה המלודית-השקטה מושרת ברכות כמעט מלוחשת היא לא רק אסתטיקה: היא המנגנון הפסיכולוגי של הדוברת. זאת לא צעקה של ביטחון  זאת לחישה של אומץ. "אני יש לי</v>
+        <v>“משוגע” של אופיר הדס הוא שיר עם לב כפול: מצד אחד – טקסט פנימי, כמעט קלסטרופובי, על אדם הסגור בתוך עצמו. מצד שני – עיבוד לטיני קצבי (בין סמבה לרומבה) שמניע את הגוף קדימה. הפער הזה הוא לא מקרי. הוא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הילה רוח – זאת השנה שלי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>בן ארצי ואהרון רזאל – תודה</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%95%d7%90%d7%94%d7%a8%d7%95%d7%9f-%d7%a8%d7%96%d7%90%d7%9c-%d7%aa%d7%95%d7%93%d7%94/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>“תודה” הוא שיר הודיה  אבל לא נאיבי.. זו אינה שמחה פשוטה, אלא הודיה שעברה דרך כאב, ספק ושבר. הדואט בין שני קולות שמגיעים מעולמות מעט שונים  – חילוני־פואטי (בן ארצי) ואמוני מובהק (אהרן רזאל) —יוצר מרחב שמחבר בין רוחניות אישית</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>בן ארצי ואהרון רזאל – תודה</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>דניאל גרנט – מיס דייזי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-14</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%92%d7%a8%d7%a0%d7%98-%d7%9e%d7%99%d7%a1-%d7%93%d7%99%d7%99%d7%96%d7%99/</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>זה לא ראפ על הצלחה – זה ראפ על הזמן שבין ההצלחות. השיר של דניאל גרנט עוסק באזור הכי פחות מדובר בקריירה: לא ההתחלה, לא הפריצה, אלא השנים האפורות באמצע, כשהכול כבר כמעט קרה… ואז נעצר. הבית הראשון מציג ביוגרפיה</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>דניאל גרנט – מיס דייזי</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>רז פרסטן – ביג</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-13</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%96-%d7%a4%d7%a8%d7%a1%d7%98%d7%9f-%d7%91%d7%99%d7%92/</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>"ביג” של רז פרסטן הוא רוק מהיר, מחוספס וכמעט פאנקי-פוסט-פאנק.  הליבה הטקסטואלית נשמעת כהצהרת דור. הוא לא מדבר על הצלחה.  הוא מדבר על התנאים להיות בכלל נשמע. הלהקה מצהירה בדף המידע כי שואבת השראה מלהקת כ-Turnstile ומ –  של Fontaines</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>רז פרסטן – ביג</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נועם קלינשטיין – אותו דבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-12</v>
-      </c>
-      <c r="C6" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%9d-%d7%a7%d7%9c%d7%99%d7%a0%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%90%d7%95%d7%aa%d7%95-%d7%93%d7%91%d7%a8/</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>נועם קלינשטיין שרה שיר פופ קצבי אולד-סקול עם דרייב של נסיעה (“driving pop”) — כלומר שיר שנשען על גרוב רציף, מרכז הרמוני יציב וקולות ליווי נשיים שעוטפים ולא שוברים את הזרימה. זה לא שיר פרידה קלאסי אלא שיר אחרי הפרידה..</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נועם קלינשטיין – אותו דבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>משה כורסיה – עומד מולך היום</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-12</v>
-      </c>
-      <c r="C7" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%9b%d7%95%d7%a8%d7%a1%d7%99%d7%94-%d7%a2%d7%95%d7%9e%d7%93-%d7%9e%d7%95%d7%9c%d7%9a-%d7%94%d7%99%d7%95%d7%9d/</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>זהו שיר תפילה במבנה של בלדה מודרנית. לא תפילה ליטורגית, אלא אישית, חשופה, כמעט יומיומית. השיר מתאר אדם שהתעייף מלהחזיק דימוי חזק כלפי חוץ,  ומבקש בפעם הראשונה לא להוכיח, אלא להשתייך. משה כורסיה מספר כי הרקע לשיר – התמודדות עם</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>משה כורסיה – עומד מולך היום</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>נתן כהן – ותגיד לי אתה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-12</v>
-      </c>
-      <c r="C8" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9f-%d7%9b%d7%94%d7%9f-%d7%95%d7%aa%d7%92%d7%99%d7%93-%d7%9c%d7%99-%d7%90%d7%aa%d7%94/</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v>נתן כהן, שבלט ב"הנשמות הטהורות" ביכולת לכתוב ולהלחין שירים עם פשטות פיוטית ("אחכה לך", "אחרי שהסירות"), ממשיך כאן קו סגנוני מוכר. השיר מדבר על זמן של עייפות תרבותית.על עולם שבו הטבע מתייבש לאט, הילדים משחקים כאילו כלום, האוויר כבד, והמבוגר</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>נתן כהן – ותגיד לי אתה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>נוגה פרידמן – עזרה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-11</v>
-      </c>
-      <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%92%d7%94-%d7%a4%d7%a8%d7%99%d7%93%d7%9e%d7%9f-%d7%a2%d7%96%d7%a8%d7%94/</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>"עזרה" ששרה נוגה פרידמן הוא שיר שקשה לנתח אותו מבלי לזכור את נסיבות כתיבתו,  אבל כוחו האמיתי הוא בכך שהוא עומד גם בלי הביוגרפיה. האובדן האישי של בן זוגה, עידו רוזנטל ז"ל, נוכח בשיר, אך הוא לא מתואר. אין אזכור</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>נוגה פרידמן – עזרה</v>
+        <v>אופיר הדס – משוגע</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופיר הדס – משוגע</v>
+        <v>פטרושקה – גלוחי העורף</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%94%d7%93%d7%a1-%d7%9e%d7%a9%d7%95%d7%92%d7%a2/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%95%d7%a9%d7%a7%d7%94-%d7%92%d7%9c%d7%95%d7%97%d7%99-%d7%94%d7%a2%d7%95%d7%a8%d7%a3/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“משוגע” של אופיר הדס הוא שיר עם לב כפול: מצד אחד – טקסט פנימי, כמעט קלסטרופובי, על אדם הסגור בתוך עצמו. מצד שני – עיבוד לטיני קצבי (בין סמבה לרומבה) שמניע את הגוף קדימה. הפער הזה הוא לא מקרי. הוא</v>
+        <v>"גלוחי העורף" של עידו פטרושקה הוא שיר עירוני לא “על העיר” אלא מתוכה.. אין כאן עמדה מוסרית ברורה, אין פתרון, אין סיפור שלם. יש אוסף מבטים קצרים, כמעט תיעודיים, שמרחפים בין חמלה לאדישות. הקול המחוספס והמקצב  הסימטרי יוצרים תחושת הליכה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופיר הדס – משוגע</v>
+        <v>פטרושקה – גלוחי העורף</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פטרושקה – גלוחי העורף</v>
+        <v>נטע ברזילי – סרנדה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%95%d7%a9%d7%a7%d7%94-%d7%92%d7%9c%d7%95%d7%97%d7%99-%d7%94%d7%a2%d7%95%d7%a8%d7%a3/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%a1%d7%a8%d7%a0%d7%93%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"גלוחי העורף" של עידו פטרושקה הוא שיר עירוני לא “על העיר” אלא מתוכה.. אין כאן עמדה מוסרית ברורה, אין פתרון, אין סיפור שלם. יש אוסף מבטים קצרים, כמעט תיעודיים, שמרחפים בין חמלה לאדישות. הקול המחוספס והמקצב  הסימטרי יוצרים תחושת הליכה</v>
+        <v>“סרנדה” ששרה נטע ברזילי היא בלדה אמוציונלית שמצליחה לעשות מהלך עדין מאוד: להישמע כמו שיר אהבה,  אבל בפועל להיות שיר על חוסר אונים בתוך אהבה. שיר של שחיקה איטית שהופך דרמה נואשת. הפער הראשון בשיר הוא פער תקשורתי: "אני יכולה לספור</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פטרושקה – גלוחי העורף</v>
+        <v>נטע ברזילי – סרנדה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נטע ברזילי – סרנדה</v>
+        <v>ישי ריבו – הנשמה לא meta</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%a1%d7%a8%d7%a0%d7%93%d7%94/</v>
+        <v>https://yosmusic.com/%d7%99%d7%a9%d7%99-%d7%a8%d7%99%d7%91%d7%95-%d7%94%d7%a0%d7%a9%d7%9e%d7%94-%d7%9c%d7%90-meta/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“סרנדה” ששרה נטע ברזילי היא בלדה אמוציונלית שמצליחה לעשות מהלך עדין מאוד: להישמע כמו שיר אהבה,  אבל בפועל להיות שיר על חוסר אונים בתוך אהבה. שיר של שחיקה איטית שהופך דרמה נואשת. הפער הראשון בשיר הוא פער תקשורתי: "אני יכולה לספור</v>
+        <v>“הנשמה לא Meta” הוא שיר אמוני מובהק  אבל שונה בנוף של ישי ריבו. במקום תפילה ישירה לאל, יש כאן פנייה לנשמה עצמה. במקום אויב רוחני מופשט  האתגר הוא עידן הרשתות. השיר מציב עימות חד: נשמה נצחית מול מציאות דיגיטלית. למה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נטע ברזילי – סרנדה</v>
+        <v>ישי ריבו – הנשמה לא meta</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ישי ריבו – הנשמה לא meta</v>
+        <v>עלמה גוב – בסיבוב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a9%d7%99-%d7%a8%d7%99%d7%91%d7%95-%d7%94%d7%a0%d7%a9%d7%9e%d7%94-%d7%9c%d7%90-meta/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%9c%d7%9e%d7%94-%d7%92%d7%95%d7%91-%d7%91%d7%a1%d7%99%d7%91%d7%95%d7%91/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“הנשמה לא Meta” הוא שיר אמוני מובהק  אבל שונה בנוף של ישי ריבו. במקום תפילה ישירה לאל, יש כאן פנייה לנשמה עצמה. במקום אויב רוחני מופשט  האתגר הוא עידן הרשתות. השיר מציב עימות חד: נשמה נצחית מול מציאות דיגיטלית. למה</v>
+        <v>“בסיבוב” ששרה עלמה גוב הוא שיר תנועה פיזית ונפשית. הוא נכתב מתוך מעבר מהמושב לתל אביב, אבל במהותו זה שיר על ניסיון לברוח ועל ההבנה שהלב נוסע יחד איתך.הקצב המהיר והאנרגיה הכמעט כבישית אינם רק תפאורה – הם חלק מהרעיון</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ישי ריבו – הנשמה לא meta</v>
+        <v>עלמה גוב – בסיבוב</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עלמה גוב – בסיבוב</v>
+        <v>קובי פרץ - אהבה אמיתית</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%9c%d7%9e%d7%94-%d7%92%d7%95%d7%91-%d7%91%d7%a1%d7%99%d7%91%d7%95%d7%91/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409612&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-17</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“בסיבוב” ששרה עלמה גוב הוא שיר תנועה פיזית ונפשית. הוא נכתב מתוך מעבר מהמושב לתל אביב, אבל במהותו זה שיר על ניסיון לברוח ועל ההבנה שהלב נוסע יחד איתך.הקצב המהיר והאנרגיה הכמעט כבישית אינם רק תפאורה – הם חלק מהרעיון</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עלמה גוב – בסיבוב</v>
+        <v>קובי פרץ - אהבה אמיתית</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>עילאי אלמקייס - שוב פרידות</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409611&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>עילאי אלמקייס - שוב פרידות</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נטע ברזילי - סרנדה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409610&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נטע ברזילי - סרנדה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נועם קלינשטיין - אותו דבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409609&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נועם קלינשטיין - אותו דבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מאיה דדון - מסיבה עצובה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409608&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מאיה דדון - מסיבה עצובה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יוסף חיים - לא אקרא לך מאמי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409607&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יוסף חיים - לא אקרא לך מאמי</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>הראל מויאל - 1990</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409606&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>הראל מויאל - 1990</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דיקלה - אין עוד מלבדך</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409605&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דיקלה - אין עוד מלבדך</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אורי כלטוב &amp; רעות שי כהן - עשרים דקות</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409604&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אורי כלטוב &amp; רעות שי כהן - עשרים דקות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי פרץ - אהבה אמיתית</v>
+        <v>תומר מתנה - עלה לי רעיון</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409612&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409617&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-17</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי פרץ - אהבה אמיתית</v>
+        <v>תומר מתנה - עלה לי רעיון</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עילאי אלמקייס - שוב פרידות</v>
+        <v>תאיר שדה - שרוטה</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409611&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409616&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-17</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עילאי אלמקייס - שוב פרידות</v>
+        <v>תאיר שדה - שרוטה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נטע ברזילי - סרנדה</v>
+        <v>ששון שאולוב - אמא</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409610&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409615&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-17</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נטע ברזילי - סרנדה</v>
+        <v>ששון שאולוב - אמא</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נועם קלינשטיין - אותו דבר</v>
+        <v>שלומי שבת - ילדותי השניה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409609&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409614&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-17</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נועם קלינשטיין - אותו דבר</v>
+        <v>שלומי שבת - ילדותי השניה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מאיה דדון - מסיבה עצובה</v>
+        <v>קובי פרץ - אוהב לנצח</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409608&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409613&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-17</v>
@@ -621,164 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מאיה דדון - מסיבה עצובה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יוסף חיים - לא אקרא לך מאמי</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409607&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יוסף חיים - לא אקרא לך מאמי</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>הראל מויאל - 1990</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409606&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>הראל מויאל - 1990</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>דיקלה - אין עוד מלבדך</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409605&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>דיקלה - אין עוד מלבדך</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אורי כלטוב &amp; רעות שי כהן - עשרים דקות</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409604&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אורי כלטוב &amp; רעות שי כהן - עשרים דקות</v>
+        <v>קובי פרץ - אוהב לנצח</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תומר מתנה - עלה לי רעיון</v>
+        <v>עמית לואיס - עוד שנייה זה נגמר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409617&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409626&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-17</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תומר מתנה - עלה לי רעיון</v>
+        <v>עמית לואיס - עוד שנייה זה נגמר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תאיר שדה - שרוטה</v>
+        <v>עלמה גוב - בסיבוב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409616&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409625&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-17</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>תאיר שדה - שרוטה</v>
+        <v>עלמה גוב - בסיבוב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ששון שאולוב - אמא</v>
+        <v>נועם בנאי - קנה סוכר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409615&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409624&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-17</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ששון שאולוב - אמא</v>
+        <v>נועם בנאי - קנה סוכר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שלומי שבת - ילדותי השניה</v>
+        <v>נוי דקל - אין לך אותי</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409614&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409623&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-17</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שלומי שבת - ילדותי השניה</v>
+        <v>נוי דקל - אין לך אותי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>קובי פרץ - אוהב לנצח</v>
+        <v>לינוי טייב - אוויר לנשום</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409613&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409622&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-17</v>
@@ -621,12 +621,164 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>קובי פרץ - אוהב לנצח</v>
+        <v>לינוי טייב - אוויר לנשום</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יהודה נר - אל תדון</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409621&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יהודה נר - אל תדון</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ג'ירפות עם ליעם חכמון - טאם טאם</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409620&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ג'ירפות עם ליעם חכמון - טאם טאם</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>בני אלבז - אמריקה זה כאן</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409619&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>בני אלבז - אמריקה זה כאן</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>בן ארצי &amp; אהרן רזאל - תודה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409618&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>בן ארצי &amp; אהרן רזאל - תודה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עמית לואיס - עוד שנייה זה נגמר</v>
+        <v>נועה קירל – או לה פופה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409626&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%90%d7%95-%d7%9c%d7%94-%d7%a4%d7%95%d7%a4%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>הביטוי “או לה פופהה” הוא תעתיק עברי של הצרפתית: Oh là là, poupée. פירושו בערך: “אוי-לה-לה, בובה!”. זה נאמר בדרך כלל בטון פלרטטני/מחמיא, כמו לומר למישהי שהיא יפה או מושכת, לפעמים קצת מוגזם או הומוריסטי. נועה קירל שרה פופ עכשווי,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עמית לואיס - עוד שנייה זה נגמר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>עלמה גוב - בסיבוב</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409625&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>עלמה גוב - בסיבוב</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נועם בנאי - קנה סוכר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409624&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נועם בנאי - קנה סוכר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נוי דקל - אין לך אותי</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409623&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נוי דקל - אין לך אותי</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>לינוי טייב - אוויר לנשום</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409622&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>לינוי טייב - אוויר לנשום</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יהודה נר - אל תדון</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409621&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יהודה נר - אל תדון</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ג'ירפות עם ליעם חכמון - טאם טאם</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409620&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ג'ירפות עם ליעם חכמון - טאם טאם</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>בני אלבז - אמריקה זה כאן</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409619&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>בני אלבז - אמריקה זה כאן</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>בן ארצי &amp; אהרן רזאל - תודה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409618&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>בן ארצי &amp; אהרן רזאל - תודה</v>
+        <v>נועה קירל – או לה פופה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועה קירל – או לה פופה</v>
+        <v>הראל סקעת איתי גלו – כתוב על הקיר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%90%d7%95-%d7%9c%d7%94-%d7%a4%d7%95%d7%a4%d7%94/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%90%d7%99%d7%aa%d7%99-%d7%92%d7%9c%d7%95-%d7%9b%d7%aa%d7%95%d7%91-%d7%a2%d7%9c-%d7%94%d7%a7%d7%99%d7%a8/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-18</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הביטוי “או לה פופהה” הוא תעתיק עברי של הצרפתית: Oh là là, poupée. פירושו בערך: “אוי-לה-לה, בובה!”. זה נאמר בדרך כלל בטון פלרטטני/מחמיא, כמו לומר למישהי שהיא יפה או מושכת, לפעמים קצת מוגזם או הומוריסטי. נועה קירל שרה פופ עכשווי,</v>
+        <v>“כתוב על הקיר”  ששר הראל סקעת הוא שיר שנע בין קלאוסטרופוביה להתפרקות משחררת, ומקבל את שיאו בהפיכה לדאנס-טראנס מרקיד בניצוחו הדי־ג’יי איתי גלו. זה  מעבר סגנוני.שמעצים דרמה נפשית שמתרחשת דרך הקצב. הטקסט מתחיל במרחב סגור מאוד. התחושה כמעט דיכאונית – חיים</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועה קירל – או לה פופה</v>
+        <v>הראל סקעת איתי גלו – כתוב על הקיר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל סקעת איתי גלו – כתוב על הקיר</v>
+        <v>זהבי עם ליאור נרקיס - Aliya</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%90%d7%99%d7%aa%d7%99-%d7%92%d7%9c%d7%95-%d7%9b%d7%aa%d7%95%d7%91-%d7%a2%d7%9c-%d7%94%d7%a7%d7%99%d7%a8/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409634&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-18</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“כתוב על הקיר”  ששר הראל סקעת הוא שיר שנע בין קלאוסטרופוביה להתפרקות משחררת, ומקבל את שיאו בהפיכה לדאנס-טראנס מרקיד בניצוחו הדי־ג’יי איתי גלו. זה  מעבר סגנוני.שמעצים דרמה נפשית שמתרחשת דרך הקצב. הטקסט מתחיל במרחב סגור מאוד. התחושה כמעט דיכאונית – חיים</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל סקעת איתי גלו – כתוב על הקיר</v>
+        <v>זהבי עם ליאור נרקיס - Aliya</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>הראל סקעת &amp; איתי גלו - כתוב על הקיר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409633&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>הראל סקעת &amp; איתי גלו - כתוב על הקיר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>דנה שלום כהן - כל בוקר לבחור</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409632&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>דנה שלום כהן - כל בוקר לבחור</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>דיז'ון - אפקט הדומינו</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409631&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>דיז'ון - אפקט הדומינו</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אסתר גד - הגעת לאן שהגעת</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409630&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אסתר גד - הגעת לאן שהגעת</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אמיר אליהו - עוברים הם החיים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409629&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אמיר אליהו - עוברים הם החיים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אור משה - לא מגיע לי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409628&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אור משה - לא מגיע לי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אביר יעקב - בוגדת</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409627&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אביר יעקב - בוגדת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זהבי עם ליאור נרקיס - Aliya</v>
+        <v>תמיר גל &amp; בני אלבז - מאמי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409634&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409641&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-18</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זהבי עם ליאור נרקיס - Aliya</v>
+        <v>תמיר גל &amp; בני אלבז - מאמי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>הראל סקעת &amp; איתי גלו - כתוב על הקיר</v>
+        <v>שי עזאני - אורח</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409633&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409640&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-18</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>הראל סקעת &amp; איתי גלו - כתוב על הקיר</v>
+        <v>שי עזאני - אורח</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דנה שלום כהן - כל בוקר לבחור</v>
+        <v>ריקיז - מלודי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409632&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409639&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-18</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דנה שלום כהן - כל בוקר לבחור</v>
+        <v>ריקיז - מלודי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>דיז'ון - אפקט הדומינו</v>
+        <v>נועה קירל - או לה פופה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409631&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409638&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-18</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>דיז'ון - אפקט הדומינו</v>
+        <v>נועה קירל - או לה פופה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אסתר גד - הגעת לאן שהגעת</v>
+        <v>נהוראי תורג'מן - בתוך הראש שלי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409630&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409637&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-18</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אסתר גד - הגעת לאן שהגעת</v>
+        <v>נהוראי תורג'מן - בתוך הראש שלי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אמיר אליהו - עוברים הם החיים</v>
+        <v>מור פדלון - חדש</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409629&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409636&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-18</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אמיר אליהו - עוברים הם החיים</v>
+        <v>מור פדלון - חדש</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אור משה - לא מגיע לי</v>
+        <v>מור מזרחי - הפסדת אותי</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409628&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409635&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-18</v>
@@ -697,50 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אור משה - לא מגיע לי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אביר יעקב - בוגדת</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409627&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אביר יעקב - בוגדת</v>
+        <v>מור מזרחי - הפסדת אותי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמיר גל &amp; בני אלבז - מאמי</v>
+        <v>פלורה – מנגינה מחייכת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409641&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%94-%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94-%d7%9e%d7%97%d7%99%d7%99%d7%9b%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>פלורה שרה שיר שמתקיים כמעט כולו במרחב עדין – לא דרמה, לא וידוי גדול, אלא תהליך פנימי. הוא נשמע כמו שיר־מסע, אבל לא מסע גיאוגרפי אלא מעבר פסיכולוגי: ממצב קפוא למצב זורם. בולט בהאזנה ראשונה הפער בין טקסט שמדבר על</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,240 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמיר גל &amp; בני אלבז - מאמי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שי עזאני - אורח</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409640&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שי עזאני - אורח</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ריקיז - מלודי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409639&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>ריקיז - מלודי</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נועה קירל - או לה פופה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409638&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נועה קירל - או לה פופה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נהוראי תורג'מן - בתוך הראש שלי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409637&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נהוראי תורג'מן - בתוך הראש שלי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>מור פדלון - חדש</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409636&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>מור פדלון - חדש</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>מור מזרחי - הפסדת אותי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409635&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>מור מזרחי - הפסדת אותי</v>
+        <v>פלורה – מנגינה מחייכת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פלורה – מנגינה מחייכת</v>
+        <v>אביגיל - באתי להפתיע</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%94-%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94-%d7%9e%d7%97%d7%99%d7%99%d7%9b%d7%aa/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409642&amp;sid=15e82b1be007fa94d4ae04510603cc18</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>פלורה שרה שיר שמתקיים כמעט כולו במרחב עדין – לא דרמה, לא וידוי גדול, אלא תהליך פנימי. הוא נשמע כמו שיר־מסע, אבל לא מסע גיאוגרפי אלא מעבר פסיכולוגי: ממצב קפוא למצב זורם. בולט בהאזנה ראשונה הפער בין טקסט שמדבר על</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פלורה – מנגינה מחייכת</v>
+        <v>אביגיל - באתי להפתיע</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביגיל - באתי להפתיע</v>
+        <v>הדר הלל - צונאמי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409642&amp;sid=15e82b1be007fa94d4ae04510603cc18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409650&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביגיל - באתי להפתיע</v>
+        <v>הדר הלל - צונאמי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>דניאל בן חיים - לבד</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409649&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>דניאל בן חיים - לבד</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>דון יצחק מזרחי - הולך באמונה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409648&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>דון יצחק מזרחי - הולך באמונה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אפיק וקנין - יש לי כמה חלומות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409647&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אפיק וקנין - יש לי כמה חלומות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אליה והב - אבא סלח לי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409646&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אליה והב - אבא סלח לי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>איתי הררי - אישה יפה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409645&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>איתי הררי - אישה יפה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אייל טויטו - הלילה הזה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409644&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אייל טויטו - הלילה הזה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אופיר סלטון - איך אתה עוד כאן</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409643&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אופיר סלטון - איך אתה עוד כאן</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הדר הלל - צונאמי</v>
+        <v>נאור גור - מחשבות אסורות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409650&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409659&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הדר הלל - צונאמי</v>
+        <v>נאור גור - מחשבות אסורות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>דניאל בן חיים - לבד</v>
+        <v>מתן טולדנו - נותן הכל מהלב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409649&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409658&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-19</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>דניאל בן חיים - לבד</v>
+        <v>מתן טולדנו - נותן הכל מהלב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דון יצחק מזרחי - הולך באמונה</v>
+        <v>מאיר אלפי - נוקאאוט</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409648&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409657&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-19</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דון יצחק מזרחי - הולך באמונה</v>
+        <v>מאיר אלפי - נוקאאוט</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אפיק וקנין - יש לי כמה חלומות</v>
+        <v>יחיאל שוקרון - התחלות חדשות</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409647&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409656&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-19</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אפיק וקנין - יש לי כמה חלומות</v>
+        <v>יחיאל שוקרון - התחלות חדשות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אליה והב - אבא סלח לי</v>
+        <v>יוסף כהן - לא טובה לי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409646&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409655&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-19</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אליה והב - אבא סלח לי</v>
+        <v>יוסף כהן - לא טובה לי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>איתי הררי - אישה יפה</v>
+        <v>חיים דדון - מדורות בלב</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409645&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409654&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-19</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>איתי הררי - אישה יפה</v>
+        <v>חיים דדון - מדורות בלב</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אייל טויטו - הלילה הזה</v>
+        <v>חיים אל - להיות אני</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409644&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409653&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-19</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אייל טויטו - הלילה הזה</v>
+        <v>חיים אל - להיות אני</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אופיר סלטון - איך אתה עוד כאן</v>
+        <v>זיו אמסילי - היינו</v>
       </c>
       <c r="B9" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409643&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409652&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-19</v>
@@ -735,12 +735,50 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אופיר סלטון - איך אתה עוד כאן</v>
+        <v>זיו אמסילי - היינו</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>הדר שושן - תפילה של מישהו אחר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409651&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>הדר שושן - תפילה של מישהו אחר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נאור גור - מחשבות אסורות</v>
+        <v>שמעון עוקשי &amp; ליאור מיארה - היא משקרת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409659&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409664&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נאור גור - מחשבות אסורות</v>
+        <v>שמעון עוקשי &amp; ליאור מיארה - היא משקרת</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מתן טולדנו - נותן הכל מהלב</v>
+        <v>שמעון טובול - אפור לבן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409658&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409663&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-19</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מתן טולדנו - נותן הכל מהלב</v>
+        <v>שמעון טובול - אפור לבן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מאיר אלפי - נוקאאוט</v>
+        <v>שלמה כהן - אמונה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409657&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409662&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-19</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מאיר אלפי - נוקאאוט</v>
+        <v>שלמה כהן - אמונה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יחיאל שוקרון - התחלות חדשות</v>
+        <v>עדן גבריאל - מה עשיתי לך</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409656&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409661&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-19</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יחיאל שוקרון - התחלות חדשות</v>
+        <v>עדן גבריאל - מה עשיתי לך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יוסף כהן - לא טובה לי</v>
+        <v>נועה חלפון - ואולי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409655&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409660&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-19</v>
@@ -621,164 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יוסף כהן - לא טובה לי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>חיים דדון - מדורות בלב</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409654&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>חיים דדון - מדורות בלב</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>חיים אל - להיות אני</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409653&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>חיים אל - להיות אני</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>זיו אמסילי - היינו</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409652&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>זיו אמסילי - היינו</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>הדר שושן - תפילה של מישהו אחר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409651&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>הדר שושן - תפילה של מישהו אחר</v>
+        <v>נועה חלפון - ואולי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון עוקשי &amp; ליאור מיארה - היא משקרת</v>
+        <v>סטטיק – מנדם‎</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409664&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%98%d7%99%d7%a7-%d7%9e%d7%a0%d7%93%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>סטטיק עושה שיר פופ-ראפ שמבוסס על ערבוב תרבויות: עברית  + סלנג לונדוני + היפ-הופ בריטי  והכול עטוף בשאלה אחת: מה קורה לאגו כשפתאום מופיע רגש אמיתי? המילה mandem – חבורת גברים מגדירה קוד גברי של כוח, סטטוס וחסינות רגשית. השיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,164 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון עוקשי &amp; ליאור מיארה - היא משקרת</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שמעון טובול - אפור לבן</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409663&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שמעון טובול - אפור לבן</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שלמה כהן - אמונה</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409662&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שלמה כהן - אמונה</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עדן גבריאל - מה עשיתי לך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409661&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עדן גבריאל - מה עשיתי לך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נועה חלפון - ואולי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409660&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נועה חלפון - ואולי</v>
+        <v>סטטיק – מנדם‎</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סטטיק – מנדם‎</v>
+        <v>נועם בתן - מדאם</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%98%d7%99%d7%a7-%d7%9e%d7%a0%d7%93%d7%9d/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=405155&amp;sid=539c4338e265962a6a59dd4295061feb</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-20</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>סטטיק עושה שיר פופ-ראפ שמבוסס על ערבוב תרבויות: עברית  + סלנג לונדוני + היפ-הופ בריטי  והכול עטוף בשאלה אחת: מה קורה לאגו כשפתאום מופיע רגש אמיתי? המילה mandem – חבורת גברים מגדירה קוד גברי של כוח, סטטוס וחסינות רגשית. השיר</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סטטיק – מנדם‎</v>
+        <v>נועם בתן - מדאם</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועם בתן - מדאם</v>
+        <v>דניאל בן חיים – לבד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=405155&amp;sid=539c4338e265962a6a59dd4295061feb</v>
+        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%91%d7%9f-%d7%97%d7%99%d7%99%d7%9d-%d7%9c%d7%91%d7%93/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>דניאל בן חיים שר שיר של כאב אישי הנובע מהצטברות רגש והופך להתפרצות קולית. השיר לא מתאר אהבה במשבר אלא את החיים אחרי, כשהרגש כבר נגמר בצד השני ונשאר רק בצד אחד. השיר בנוי סביב פעולה חוזרת – “תקחי ממני”.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועם בתן - מדאם</v>
+        <v>דניאל בן חיים – לבד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דניאל בן חיים – לבד</v>
+        <v>רונן לוגסי - מחרוזת שקטים 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%91%d7%9f-%d7%97%d7%99%d7%99%d7%9d-%d7%9c%d7%91%d7%93/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409702&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-21</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>דניאל בן חיים שר שיר של כאב אישי הנובע מהצטברות רגש והופך להתפרצות קולית. השיר לא מתאר אהבה במשבר אלא את החיים אחרי, כשהרגש כבר נגמר בצד השני ונשאר רק בצד אחד. השיר בנוי סביב פעולה חוזרת – “תקחי ממני”.</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דניאל בן חיים – לבד</v>
+        <v>רונן לוגסי - מחרוזת שקטים 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ראובן המלאך - מחרוזת השירים של פעם 2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409701&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>ראובן המלאך - מחרוזת השירים של פעם 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>פארידה - מחרוזת קווקזית 2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409700&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>פארידה - מחרוזת קווקזית 2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ניראל ארגוב - מחרוזת פורים 2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409699&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ניראל ארגוב - מחרוזת פורים 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>נופר בטאט - מחרוזת טברנה 2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409698&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>נופר בטאט - מחרוזת טברנה 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>חיים אביטל - מחרוזת שקטים חלק א 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409697&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>חיים אביטל - מחרוזת שקטים חלק א 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דודו קדוש - מחרוזת שקטים כבו הכוכבים 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409696&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דודו קדוש - מחרוזת שקטים כבו הכוכבים 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דודו בן חמו - מחרוזת מי שלא מוחא כפיים 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409695&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דודו בן חמו - מחרוזת מי שלא מוחא כפיים 2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלינור חלילוב - מחרוזת 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409694&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלינור חלילוב - מחרוזת 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>איציק הג'ינג'י - מחרוזת מאמי 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409693&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>איציק הג'ינג'י - מחרוזת מאמי 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>איציק הג'ינג'י - מחרוזת כאב ראש 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409692&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>איציק הג'ינג'י - מחרוזת כאב ראש 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>